--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00966B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00966B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{592BA163-53F0-444C-8616-5ED3F71F9D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47424430-134B-4FA6-A17A-E7B5EF251EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{35E5881E-0A4A-45B4-A9BE-38DC1190833E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{3CE98159-AC66-47E2-8F86-DBC58E4C2BDB}"/>
   </bookViews>
   <sheets>
     <sheet name="00966B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1546,24 +1546,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFB0DAD-25E8-43D3-8B29-CC2CBF158661}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65FF7D8-1F43-416B-BC2C-5012AFEB9A68}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1591,7 +1592,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1621,7 +1622,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1667,7 +1668,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1717,7 +1718,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1771,7 +1772,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1797,7 +1798,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1853,7 +1854,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1909,7 +1910,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
@@ -1965,7 +1966,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="49">
         <v>2025</v>
       </c>
@@ -2019,7 +2020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2075,7 +2076,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2131,7 +2132,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2187,7 +2188,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2243,7 +2244,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2299,7 +2300,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2355,7 +2356,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2411,7 +2412,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2467,7 +2468,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2523,7 +2524,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2579,7 +2580,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="51" t="s">
         <v>53</v>
       </c>
